--- a/CvsuTanzaSampleAccounts.xlsx
+++ b/CvsuTanzaSampleAccounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikha\Desktop\ABACUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424876F4-362E-4750-A399-D258938B6F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3C4FC0-9F2A-4557-B341-E69052EF3ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C30ACE0C-4347-42EE-84D5-1D11B2310907}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>tc.marionadam.purugganan@cvsu.edu.ph</t>
   </si>
@@ -67,13 +67,22 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>jhanzy.samar@cvsu.edu.ph</t>
+  </si>
+  <si>
+    <t>mikhaelgarcia</t>
+  </si>
+  <si>
+    <t>jhanzy@cvsu.edu.ph</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,12 +102,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,7 +128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -133,9 +136,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -451,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC96DCD-8156-4E2B-9C70-07A69F6D2F30}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -531,8 +535,28 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="1">
+        <v>202218637</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>123456789</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>123456789</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -544,8 +568,10 @@
     <hyperlink ref="B3" r:id="rId6" xr:uid="{7E1B69B9-83A0-47E7-97C4-5C50EC2987E8}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{FF18DB3C-E31C-461F-8932-8E9D79D08793}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{4D68CDE7-C917-4A04-BBEE-AE7959346F48}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{DFB06D04-4C87-4CE9-A418-B1346AD537FD}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{FF4FBCA4-960F-49FD-8747-B5862DC46939}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>
--- a/CvsuTanzaSampleAccounts.xlsx
+++ b/CvsuTanzaSampleAccounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikha\Desktop\ABACUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3C4FC0-9F2A-4557-B341-E69052EF3ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24979C01-0773-4740-8B9C-5494587FFBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C30ACE0C-4347-42EE-84D5-1D11B2310907}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>tc.marionadam.purugganan@cvsu.edu.ph</t>
   </si>
@@ -69,13 +69,31 @@
     <t>Email</t>
   </si>
   <si>
-    <t>jhanzy.samar@cvsu.edu.ph</t>
-  </si>
-  <si>
-    <t>mikhaelgarcia</t>
-  </si>
-  <si>
-    <t>jhanzy@cvsu.edu.ph</t>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>purugganan, marion adam c.</t>
+  </si>
+  <si>
+    <t>gadon, vincent eyron h.</t>
+  </si>
+  <si>
+    <t>maglaway, niesha anne c.</t>
+  </si>
+  <si>
+    <t>gado, paul bryan m.</t>
+  </si>
+  <si>
+    <t>pagota, mary anne a.</t>
+  </si>
+  <si>
+    <t>rapis, reymond</t>
+  </si>
+  <si>
+    <t>samar, jhanzy o.</t>
+  </si>
+  <si>
+    <t>garcia, mikhael v.</t>
   </si>
 </sst>
 </file>
@@ -128,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -140,6 +158,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -455,108 +476,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC96DCD-8156-4E2B-9C70-07A69F6D2F30}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="36.6328125" customWidth="1"/>
+    <col min="3" max="3" width="28.90625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>202218701</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>202218631</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>202218660</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>202218810</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>202218859</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>202218867</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>202218715</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>202218637</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>202218637</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>123456789</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>123456789</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -568,10 +604,8 @@
     <hyperlink ref="B3" r:id="rId6" xr:uid="{7E1B69B9-83A0-47E7-97C4-5C50EC2987E8}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{FF18DB3C-E31C-461F-8932-8E9D79D08793}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{4D68CDE7-C917-4A04-BBEE-AE7959346F48}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{DFB06D04-4C87-4CE9-A418-B1346AD537FD}"/>
-    <hyperlink ref="B12" r:id="rId10" xr:uid="{FF4FBCA4-960F-49FD-8747-B5862DC46939}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId11"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>
--- a/CvsuTanzaSampleAccounts.xlsx
+++ b/CvsuTanzaSampleAccounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikha\Desktop\ABACUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24979C01-0773-4740-8B9C-5494587FFBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F454C16A-DA77-43A5-9E3B-5EA565A5215F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C30ACE0C-4347-42EE-84D5-1D11B2310907}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>tc.marionadam.purugganan@cvsu.edu.ph</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Student Name</t>
   </si>
   <si>
-    <t>purugganan, marion adam c.</t>
-  </si>
-  <si>
     <t>gadon, vincent eyron h.</t>
   </si>
   <si>
@@ -94,6 +91,15 @@
   </si>
   <si>
     <t>garcia, mikhael v.</t>
+  </si>
+  <si>
+    <t>purugganan, marion adam s.</t>
+  </si>
+  <si>
+    <t>tc.jhanzy.onrada@cvsu.edu.ph</t>
+  </si>
+  <si>
+    <t>onrada, jhanzy s.</t>
   </si>
 </sst>
 </file>
@@ -503,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -514,7 +520,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -525,7 +531,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -536,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -547,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -558,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -569,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -580,12 +586,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="1">
+        <v>251118928</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
@@ -604,8 +617,9 @@
     <hyperlink ref="B3" r:id="rId6" xr:uid="{7E1B69B9-83A0-47E7-97C4-5C50EC2987E8}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{FF18DB3C-E31C-461F-8932-8E9D79D08793}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{4D68CDE7-C917-4A04-BBEE-AE7959346F48}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{8802843F-C7CA-495B-ACDD-962727AB794D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
 </worksheet>
 </file>
--- a/CvsuTanzaSampleAccounts.xlsx
+++ b/CvsuTanzaSampleAccounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikha\Desktop\ABACUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F454C16A-DA77-43A5-9E3B-5EA565A5215F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C11479E-9FB6-4DD8-8FA0-4708FC2169FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C30ACE0C-4347-42EE-84D5-1D11B2310907}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>tc.marionadam.purugganan@cvsu.edu.ph</t>
   </si>
@@ -96,17 +96,113 @@
     <t>purugganan, marion adam s.</t>
   </si>
   <si>
-    <t>tc.jhanzy.onrada@cvsu.edu.ph</t>
-  </si>
-  <si>
-    <t>onrada, jhanzy s.</t>
+    <t>Student First Name</t>
+  </si>
+  <si>
+    <t>Student Middle Name</t>
+  </si>
+  <si>
+    <t>Student Last Name</t>
+  </si>
+  <si>
+    <t>Marion Adam</t>
+  </si>
+  <si>
+    <t>S.</t>
+  </si>
+  <si>
+    <t>Purugganan</t>
+  </si>
+  <si>
+    <t>Vincent Eyron</t>
+  </si>
+  <si>
+    <t>H.</t>
+  </si>
+  <si>
+    <t>Gadon</t>
+  </si>
+  <si>
+    <t>Niesha Anne</t>
+  </si>
+  <si>
+    <t>C.</t>
+  </si>
+  <si>
+    <t>Maglaway</t>
+  </si>
+  <si>
+    <t>Paul Bryan</t>
+  </si>
+  <si>
+    <t>M.</t>
+  </si>
+  <si>
+    <t>Gado</t>
+  </si>
+  <si>
+    <t>Mary Anne</t>
+  </si>
+  <si>
+    <t>A.</t>
+  </si>
+  <si>
+    <t>Pagota</t>
+  </si>
+  <si>
+    <t>Reymond</t>
+  </si>
+  <si>
+    <t>Rapis</t>
+  </si>
+  <si>
+    <t>Mikhael</t>
+  </si>
+  <si>
+    <t>V.</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>Jhanzy</t>
+  </si>
+  <si>
+    <t>O.</t>
+  </si>
+  <si>
+    <t>Samar</t>
+  </si>
+  <si>
+    <t>Marion Adam S. Purugganan</t>
+  </si>
+  <si>
+    <t>Vincent Eyron H. Gadon</t>
+  </si>
+  <si>
+    <t>Niesha Anne C. Maglaway</t>
+  </si>
+  <si>
+    <t>Paul Bryan M. Gado</t>
+  </si>
+  <si>
+    <t>Mary Anne A. Pagota</t>
+  </si>
+  <si>
+    <t>Reymond Rapis</t>
+  </si>
+  <si>
+    <t>Jhanzy O. Samar</t>
+  </si>
+  <si>
+    <t>Mikhael V. Garcia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +222,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -160,11 +262,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -482,130 +584,247 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC96DCD-8156-4E2B-9C70-07A69F6D2F30}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="36.6328125" customWidth="1"/>
-    <col min="3" max="3" width="28.90625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="28.90625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>202218701</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>202218631</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>202218660</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>202218810</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>202218859</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E6" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>202218867</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E7" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>202218715</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E8" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>202218637</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>251118928</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="E9" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -617,9 +836,8 @@
     <hyperlink ref="B3" r:id="rId6" xr:uid="{7E1B69B9-83A0-47E7-97C4-5C50EC2987E8}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{FF18DB3C-E31C-461F-8932-8E9D79D08793}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{4D68CDE7-C917-4A04-BBEE-AE7959346F48}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{8802843F-C7CA-495B-ACDD-962727AB794D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>